--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28890,7 +28890,7 @@
         <v>96909251</v>
       </c>
       <c r="B253" t="n">
-        <v>56502</v>
+        <v>56503</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY253"/>
+  <dimension ref="A1:AY256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28987,6 +28987,327 @@
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>130581319</v>
+      </c>
+      <c r="B254" t="n">
+        <v>89125</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>510</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Lulevardo, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>514117</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7205717</v>
+      </c>
+      <c r="S254" t="n">
+        <v>25</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>130581317</v>
+      </c>
+      <c r="B255" t="n">
+        <v>83027</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Lulevardo, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>513976</v>
+      </c>
+      <c r="R255" t="n">
+        <v>7205648</v>
+      </c>
+      <c r="S255" t="n">
+        <v>25</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>130581318</v>
+      </c>
+      <c r="B256" t="n">
+        <v>79183</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Lulevardo, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>513975</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7205650</v>
+      </c>
+      <c r="S256" t="n">
+        <v>25</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>130581318</v>
       </c>
       <c r="B256" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89151</v>
+        <v>89152</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89152</v>
+        <v>89153</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89153</v>
+        <v>89155</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>130581318</v>
       </c>
       <c r="B256" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89155</v>
+        <v>89167</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83057</v>
+        <v>83065</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>130581318</v>
       </c>
       <c r="B256" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89167</v>
+        <v>89168</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83065</v>
+        <v>83066</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>130581318</v>
       </c>
       <c r="B256" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -28992,7 +28992,7 @@
         <v>130581319</v>
       </c>
       <c r="B254" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>130581317</v>
       </c>
       <c r="B255" t="n">
-        <v>83066</v>
+        <v>83067</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>130581318</v>
       </c>
       <c r="B256" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>

--- a/artfynd/A 60433-2021 artfynd.xlsx
+++ b/artfynd/A 60433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY237"/>
+  <dimension ref="A1:AY238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96909175</v>
+        <v>134713794</v>
       </c>
       <c r="B46" t="n">
-        <v>58592</v>
+        <v>57624</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4954,21 +4954,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102125</v>
+        <v>100063</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4976,24 +4976,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Middagskullen, Saxnäs, Ås lm</t>
+          <t>Getarudden, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514391</v>
+        <v>514382</v>
       </c>
       <c r="R46" t="n">
-        <v>7206318</v>
+        <v>7206366</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5017,12 +5020,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5037,39 +5050,39 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96909274</v>
+        <v>96909175</v>
       </c>
       <c r="B47" t="n">
-        <v>58057</v>
+        <v>58592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>102125</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5079,12 +5092,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5093,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514377</v>
+        <v>514391</v>
       </c>
       <c r="R47" t="n">
-        <v>7206336</v>
+        <v>7206318</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5155,44 +5168,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>101717629</v>
+        <v>96909274</v>
       </c>
       <c r="B48" t="n">
-        <v>58817</v>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208249</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5201,10 +5212,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514501</v>
+        <v>514377</v>
       </c>
       <c r="R48" t="n">
-        <v>7206324</v>
+        <v>7206336</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5231,22 +5242,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>01:34</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>01:34</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5273,10 +5274,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96909243</v>
+        <v>101717629</v>
       </c>
       <c r="B49" t="n">
-        <v>97983</v>
+        <v>58817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5284,34 +5285,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514305</v>
+        <v>514501</v>
       </c>
       <c r="R49" t="n">
-        <v>7206166</v>
+        <v>7206324</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5338,12 +5350,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>01:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>01:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5370,7 +5392,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96909244</v>
+        <v>96909243</v>
       </c>
       <c r="B50" t="n">
         <v>97983</v>
@@ -5405,10 +5427,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514296</v>
+        <v>514305</v>
       </c>
       <c r="R50" t="n">
-        <v>7206165</v>
+        <v>7206166</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5467,7 +5489,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96909245</v>
+        <v>96909244</v>
       </c>
       <c r="B51" t="n">
         <v>97983</v>
@@ -5502,10 +5524,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514375</v>
+        <v>514296</v>
       </c>
       <c r="R51" t="n">
-        <v>7206333</v>
+        <v>7206165</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5564,7 +5586,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96909248</v>
+        <v>96909245</v>
       </c>
       <c r="B52" t="n">
         <v>97983</v>
@@ -5599,10 +5621,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514299</v>
+        <v>514375</v>
       </c>
       <c r="R52" t="n">
-        <v>7206116</v>
+        <v>7206333</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5629,12 +5651,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5654,39 +5676,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96909405</v>
+        <v>96909248</v>
       </c>
       <c r="B53" t="n">
-        <v>83299</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5696,10 +5718,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513867</v>
+        <v>514299</v>
       </c>
       <c r="R53" t="n">
-        <v>7206217</v>
+        <v>7206116</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5726,12 +5748,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5751,39 +5773,39 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96909134</v>
+        <v>96909405</v>
       </c>
       <c r="B54" t="n">
-        <v>78350</v>
+        <v>83299</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5793,10 +5815,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514140</v>
+        <v>513867</v>
       </c>
       <c r="R54" t="n">
-        <v>7206229</v>
+        <v>7206217</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5855,10 +5877,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96909265</v>
+        <v>96909134</v>
       </c>
       <c r="B55" t="n">
-        <v>78686</v>
+        <v>78350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5866,21 +5888,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>498</v>
+        <v>314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5890,10 +5912,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513999</v>
+        <v>514140</v>
       </c>
       <c r="R55" t="n">
-        <v>7206182</v>
+        <v>7206229</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5952,7 +5974,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>96909266</v>
+        <v>96909265</v>
       </c>
       <c r="B56" t="n">
         <v>78686</v>
@@ -5987,10 +6009,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513924</v>
+        <v>513999</v>
       </c>
       <c r="R56" t="n">
-        <v>7205719</v>
+        <v>7206182</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6017,12 +6039,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6049,7 +6071,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96909267</v>
+        <v>96909266</v>
       </c>
       <c r="B57" t="n">
         <v>78686</v>
@@ -6084,10 +6106,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513926</v>
+        <v>513924</v>
       </c>
       <c r="R57" t="n">
-        <v>7206084</v>
+        <v>7205719</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6139,14 +6161,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96909268</v>
+        <v>96909267</v>
       </c>
       <c r="B58" t="n">
         <v>78686</v>
@@ -6181,10 +6203,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513971</v>
+        <v>513926</v>
       </c>
       <c r="R58" t="n">
-        <v>7206114</v>
+        <v>7206084</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6243,7 +6265,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>96909269</v>
+        <v>96909268</v>
       </c>
       <c r="B59" t="n">
         <v>78686</v>
@@ -6278,10 +6300,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514038</v>
+        <v>513971</v>
       </c>
       <c r="R59" t="n">
-        <v>7206010</v>
+        <v>7206114</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6340,7 +6362,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>96909270</v>
+        <v>96909269</v>
       </c>
       <c r="B60" t="n">
         <v>78686</v>
@@ -6375,10 +6397,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513910</v>
+        <v>514038</v>
       </c>
       <c r="R60" t="n">
-        <v>7205991</v>
+        <v>7206010</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6437,7 +6459,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>96909271</v>
+        <v>96909270</v>
       </c>
       <c r="B61" t="n">
         <v>78686</v>
@@ -6472,10 +6494,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513973</v>
+        <v>513910</v>
       </c>
       <c r="R61" t="n">
-        <v>7205987</v>
+        <v>7205991</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6534,7 +6556,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96909272</v>
+        <v>96909271</v>
       </c>
       <c r="B62" t="n">
         <v>78686</v>
@@ -6569,10 +6591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514335</v>
+        <v>513973</v>
       </c>
       <c r="R62" t="n">
-        <v>7206057</v>
+        <v>7205987</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6631,7 +6653,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>98158642</v>
+        <v>96909272</v>
       </c>
       <c r="B63" t="n">
         <v>78686</v>
@@ -6666,10 +6688,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514201</v>
+        <v>514335</v>
       </c>
       <c r="R63" t="n">
-        <v>7205600</v>
+        <v>7206057</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6696,22 +6718,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6722,21 +6734,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -6746,39 +6743,39 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>96909393</v>
+        <v>98158642</v>
       </c>
       <c r="B64" t="n">
-        <v>89292</v>
+        <v>78686</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6788,10 +6785,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513937</v>
+        <v>514201</v>
       </c>
       <c r="R64" t="n">
-        <v>7206266</v>
+        <v>7205600</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,12 +6815,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6834,6 +6841,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -6843,14 +6865,14 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96909394</v>
+        <v>96909393</v>
       </c>
       <c r="B65" t="n">
         <v>89292</v>
@@ -6885,10 +6907,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513876</v>
+        <v>513937</v>
       </c>
       <c r="R65" t="n">
-        <v>7206217</v>
+        <v>7206266</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6947,7 +6969,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>96909395</v>
+        <v>96909394</v>
       </c>
       <c r="B66" t="n">
         <v>89292</v>
@@ -6982,10 +7004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514011</v>
+        <v>513876</v>
       </c>
       <c r="R66" t="n">
-        <v>7205691</v>
+        <v>7206217</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,12 +7034,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7044,7 +7066,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96909396</v>
+        <v>96909395</v>
       </c>
       <c r="B67" t="n">
         <v>89292</v>
@@ -7079,10 +7101,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514045</v>
+        <v>514011</v>
       </c>
       <c r="R67" t="n">
-        <v>7205699</v>
+        <v>7205691</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7141,7 +7163,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96909397</v>
+        <v>96909396</v>
       </c>
       <c r="B68" t="n">
         <v>89292</v>
@@ -7176,10 +7198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514372</v>
+        <v>514045</v>
       </c>
       <c r="R68" t="n">
-        <v>7205998</v>
+        <v>7205699</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7238,7 +7260,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96909398</v>
+        <v>96909397</v>
       </c>
       <c r="B69" t="n">
         <v>89292</v>
@@ -7273,10 +7295,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514150</v>
+        <v>514372</v>
       </c>
       <c r="R69" t="n">
-        <v>7205873</v>
+        <v>7205998</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7335,7 +7357,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96909399</v>
+        <v>96909398</v>
       </c>
       <c r="B70" t="n">
         <v>89292</v>
@@ -7370,10 +7392,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513963</v>
+        <v>514150</v>
       </c>
       <c r="R70" t="n">
-        <v>7206098</v>
+        <v>7205873</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7425,14 +7447,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96909400</v>
+        <v>96909399</v>
       </c>
       <c r="B71" t="n">
         <v>89292</v>
@@ -7467,10 +7489,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513983</v>
+        <v>513963</v>
       </c>
       <c r="R71" t="n">
-        <v>7206122</v>
+        <v>7206098</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7529,7 +7551,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130581319</v>
+        <v>96909400</v>
       </c>
       <c r="B72" t="n">
         <v>89292</v>
@@ -7560,14 +7582,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lulevardo, Ås lm</t>
+          <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>514117</v>
+        <v>513983</v>
       </c>
       <c r="R72" t="n">
-        <v>7205717</v>
+        <v>7206122</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,22 +7616,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7629,17 +7641,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>96909236</v>
+        <v>130581319</v>
       </c>
       <c r="B73" t="n">
-        <v>92208</v>
+        <v>89292</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7647,34 +7659,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Middagskullen, Saxnäs, Ås lm</t>
+          <t>Lulevardo, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514080</v>
+        <v>514117</v>
       </c>
       <c r="R73" t="n">
-        <v>7206172</v>
+        <v>7205717</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7701,12 +7713,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7733,7 +7755,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96909237</v>
+        <v>96909236</v>
       </c>
       <c r="B74" t="n">
         <v>92208</v>
@@ -7768,10 +7790,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513880</v>
+        <v>514080</v>
       </c>
       <c r="R74" t="n">
-        <v>7206315</v>
+        <v>7206172</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7830,7 +7852,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>96909238</v>
+        <v>96909237</v>
       </c>
       <c r="B75" t="n">
         <v>92208</v>
@@ -7865,10 +7887,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>514019</v>
+        <v>513880</v>
       </c>
       <c r="R75" t="n">
-        <v>7206185</v>
+        <v>7206315</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7927,7 +7949,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96909239</v>
+        <v>96909238</v>
       </c>
       <c r="B76" t="n">
         <v>92208</v>
@@ -7962,10 +7984,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>513969</v>
+        <v>514019</v>
       </c>
       <c r="R76" t="n">
-        <v>7206232</v>
+        <v>7206185</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8024,7 +8046,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>96909240</v>
+        <v>96909239</v>
       </c>
       <c r="B77" t="n">
         <v>92208</v>
@@ -8059,10 +8081,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>514263</v>
+        <v>513969</v>
       </c>
       <c r="R77" t="n">
-        <v>7206107</v>
+        <v>7206232</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8089,12 +8111,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8114,14 +8136,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>96909241</v>
+        <v>96909240</v>
       </c>
       <c r="B78" t="n">
         <v>92208</v>
@@ -8156,10 +8178,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>514060</v>
+        <v>514263</v>
       </c>
       <c r="R78" t="n">
-        <v>7206096</v>
+        <v>7206107</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8218,10 +8240,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>96909283</v>
+        <v>96909241</v>
       </c>
       <c r="B79" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8229,21 +8251,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8253,10 +8275,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>514324</v>
+        <v>514060</v>
       </c>
       <c r="R79" t="n">
-        <v>7205949</v>
+        <v>7206096</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8308,14 +8330,14 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>96909284</v>
+        <v>96909283</v>
       </c>
       <c r="B80" t="n">
         <v>79406</v>
@@ -8350,10 +8372,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>514154</v>
+        <v>514324</v>
       </c>
       <c r="R80" t="n">
-        <v>7205997</v>
+        <v>7205949</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8405,14 +8427,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>96909285</v>
+        <v>96909284</v>
       </c>
       <c r="B81" t="n">
         <v>79406</v>
@@ -8447,10 +8469,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>513909</v>
+        <v>514154</v>
       </c>
       <c r="R81" t="n">
-        <v>7205989</v>
+        <v>7205997</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8509,7 +8531,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>96909286</v>
+        <v>96909285</v>
       </c>
       <c r="B82" t="n">
         <v>79406</v>
@@ -8544,10 +8566,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>514274</v>
+        <v>513909</v>
       </c>
       <c r="R82" t="n">
-        <v>7206029</v>
+        <v>7205989</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8606,7 +8628,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>96909287</v>
+        <v>96909286</v>
       </c>
       <c r="B83" t="n">
         <v>79406</v>
@@ -8641,10 +8663,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>514241</v>
+        <v>514274</v>
       </c>
       <c r="R83" t="n">
-        <v>7206030</v>
+        <v>7206029</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8703,7 +8725,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96909288</v>
+        <v>96909287</v>
       </c>
       <c r="B84" t="n">
         <v>79406</v>
@@ -8738,10 +8760,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>514303</v>
+        <v>514241</v>
       </c>
       <c r="R84" t="n">
-        <v>7206036</v>
+        <v>7206030</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -8800,32 +8822,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>96909177</v>
+        <v>96909288</v>
       </c>
       <c r="B85" t="n">
-        <v>92721</v>
+        <v>79406</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8835,10 +8857,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>514039</v>
+        <v>514303</v>
       </c>
       <c r="R85" t="n">
-        <v>7206239</v>
+        <v>7206036</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -8865,12 +8887,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8890,39 +8912,39 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>96909292</v>
+        <v>96909177</v>
       </c>
       <c r="B86" t="n">
-        <v>91905</v>
+        <v>92721</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8932,10 +8954,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>514108</v>
+        <v>514039</v>
       </c>
       <c r="R86" t="n">
-        <v>7206220</v>
+        <v>7206239</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -8994,7 +9016,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>96909293</v>
+        <v>96909292</v>
       </c>
       <c r="B87" t="n">
         <v>91905</v>
@@ -9029,10 +9051,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>513969</v>
+        <v>514108</v>
       </c>
       <c r="R87" t="n">
-        <v>7206232</v>
+        <v>7206220</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9091,10 +9113,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>96909151</v>
+        <v>96909293</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9102,21 +9124,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9188,7 +9210,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>96909153</v>
+        <v>96909151</v>
       </c>
       <c r="B89" t="n">
         <v>91909</v>
@@ -9223,10 +9245,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>514199</v>
+        <v>513969</v>
       </c>
       <c r="R89" t="n">
-        <v>7206171</v>
+        <v>7206232</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9285,7 +9307,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96909156</v>
+        <v>96909153</v>
       </c>
       <c r="B90" t="n">
         <v>91909</v>
@@ -9320,10 +9342,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>514019</v>
+        <v>514199</v>
       </c>
       <c r="R90" t="n">
-        <v>7206185</v>
+        <v>7206171</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9382,7 +9404,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>96909157</v>
+        <v>96909156</v>
       </c>
       <c r="B91" t="n">
         <v>91909</v>
@@ -9417,10 +9439,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>513881</v>
+        <v>514019</v>
       </c>
       <c r="R91" t="n">
-        <v>7206316</v>
+        <v>7206185</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9479,7 +9501,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>96909158</v>
+        <v>96909157</v>
       </c>
       <c r="B92" t="n">
         <v>91909</v>
@@ -9514,10 +9536,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>513857</v>
+        <v>513881</v>
       </c>
       <c r="R92" t="n">
-        <v>7206297</v>
+        <v>7206316</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9576,7 +9598,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>96909159</v>
+        <v>96909158</v>
       </c>
       <c r="B93" t="n">
         <v>91909</v>
@@ -9611,10 +9633,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>514085</v>
+        <v>513857</v>
       </c>
       <c r="R93" t="n">
-        <v>7206229</v>
+        <v>7206297</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9673,7 +9695,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96909160</v>
+        <v>96909159</v>
       </c>
       <c r="B94" t="n">
         <v>91909</v>
@@ -9708,10 +9730,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>513891</v>
+        <v>514085</v>
       </c>
       <c r="R94" t="n">
-        <v>7206055</v>
+        <v>7206229</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9738,12 +9760,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9763,14 +9785,14 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>96909161</v>
+        <v>96909160</v>
       </c>
       <c r="B95" t="n">
         <v>91909</v>
@@ -9805,10 +9827,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>514061</v>
+        <v>513891</v>
       </c>
       <c r="R95" t="n">
-        <v>7206097</v>
+        <v>7206055</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -9867,32 +9889,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>96909307</v>
+        <v>96909161</v>
       </c>
       <c r="B96" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9902,10 +9924,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>514049</v>
+        <v>514061</v>
       </c>
       <c r="R96" t="n">
-        <v>7206223</v>
+        <v>7206097</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -9932,12 +9954,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9957,14 +9979,14 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96909308</v>
+        <v>96909307</v>
       </c>
       <c r="B97" t="n">
         <v>91923</v>
@@ -9999,10 +10021,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>514099</v>
+        <v>514049</v>
       </c>
       <c r="R97" t="n">
-        <v>7205731</v>
+        <v>7206223</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10029,12 +10051,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10061,7 +10083,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96909310</v>
+        <v>96909308</v>
       </c>
       <c r="B98" t="n">
         <v>91923</v>
@@ -10096,10 +10118,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>513891</v>
+        <v>514099</v>
       </c>
       <c r="R98" t="n">
-        <v>7206055</v>
+        <v>7205731</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10151,14 +10173,14 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96909311</v>
+        <v>96909310</v>
       </c>
       <c r="B99" t="n">
         <v>91923</v>
@@ -10193,10 +10215,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>514011</v>
+        <v>513891</v>
       </c>
       <c r="R99" t="n">
-        <v>7206126</v>
+        <v>7206055</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10255,7 +10277,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>96909312</v>
+        <v>96909311</v>
       </c>
       <c r="B100" t="n">
         <v>91923</v>
@@ -10290,10 +10312,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>514022</v>
+        <v>514011</v>
       </c>
       <c r="R100" t="n">
-        <v>7206003</v>
+        <v>7206126</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10352,7 +10374,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>96909313</v>
+        <v>96909312</v>
       </c>
       <c r="B101" t="n">
         <v>91923</v>
@@ -10387,10 +10409,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>514074</v>
+        <v>514022</v>
       </c>
       <c r="R101" t="n">
-        <v>7205988</v>
+        <v>7206003</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10449,7 +10471,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>96909314</v>
+        <v>96909313</v>
       </c>
       <c r="B102" t="n">
         <v>91923</v>
@@ -10484,10 +10506,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>514279</v>
+        <v>514074</v>
       </c>
       <c r="R102" t="n">
-        <v>7206053</v>
+        <v>7205988</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10546,32 +10568,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>96909231</v>
+        <v>96909314</v>
       </c>
       <c r="B103" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10581,10 +10603,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>514197</v>
+        <v>514279</v>
       </c>
       <c r="R103" t="n">
-        <v>7206179</v>
+        <v>7206053</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10611,12 +10633,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10636,14 +10658,14 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>96909232</v>
+        <v>96909231</v>
       </c>
       <c r="B104" t="n">
         <v>92369</v>
@@ -10678,10 +10700,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>514020</v>
+        <v>514197</v>
       </c>
       <c r="R104" t="n">
-        <v>7206185</v>
+        <v>7206179</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10740,7 +10762,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>96909233</v>
+        <v>96909232</v>
       </c>
       <c r="B105" t="n">
         <v>92369</v>
@@ -10775,10 +10797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>514085</v>
+        <v>514020</v>
       </c>
       <c r="R105" t="n">
-        <v>7206234</v>
+        <v>7206185</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10837,7 +10859,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>96909234</v>
+        <v>96909233</v>
       </c>
       <c r="B106" t="n">
         <v>92369</v>
@@ -10866,19 +10888,16 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>514263</v>
+        <v>514085</v>
       </c>
       <c r="R106" t="n">
-        <v>7206106</v>
+        <v>7206234</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -10905,12 +10924,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10919,7 +10938,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10931,14 +10949,14 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>96909235</v>
+        <v>96909234</v>
       </c>
       <c r="B107" t="n">
         <v>92369</v>
@@ -10967,16 +10985,19 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>514061</v>
+        <v>514263</v>
       </c>
       <c r="R107" t="n">
-        <v>7206097</v>
+        <v>7206106</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11017,6 +11038,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11035,10 +11057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>96909376</v>
+        <v>96909235</v>
       </c>
       <c r="B108" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11046,21 +11068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11070,10 +11092,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>513777</v>
+        <v>514061</v>
       </c>
       <c r="R108" t="n">
-        <v>7206261</v>
+        <v>7206097</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11100,12 +11122,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11125,14 +11147,14 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>96909377</v>
+        <v>96909376</v>
       </c>
       <c r="B109" t="n">
         <v>83173</v>
@@ -11167,10 +11189,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>514375</v>
+        <v>513777</v>
       </c>
       <c r="R109" t="n">
-        <v>7206015</v>
+        <v>7206261</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11197,12 +11219,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11229,7 +11251,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>96909378</v>
+        <v>96909377</v>
       </c>
       <c r="B110" t="n">
         <v>83173</v>
@@ -11264,10 +11286,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>514213</v>
+        <v>514375</v>
       </c>
       <c r="R110" t="n">
-        <v>7205897</v>
+        <v>7206015</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11326,7 +11348,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>96909379</v>
+        <v>96909378</v>
       </c>
       <c r="B111" t="n">
         <v>83173</v>
@@ -11361,10 +11383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>513895</v>
+        <v>514213</v>
       </c>
       <c r="R111" t="n">
-        <v>7205980</v>
+        <v>7205897</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11416,14 +11438,14 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>96909380</v>
+        <v>96909379</v>
       </c>
       <c r="B112" t="n">
         <v>83173</v>
@@ -11458,10 +11480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>513867</v>
+        <v>513895</v>
       </c>
       <c r="R112" t="n">
-        <v>7205991</v>
+        <v>7205980</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -11520,7 +11542,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>96909381</v>
+        <v>96909380</v>
       </c>
       <c r="B113" t="n">
         <v>83173</v>
@@ -11555,10 +11577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>514190</v>
+        <v>513867</v>
       </c>
       <c r="R113" t="n">
-        <v>7205971</v>
+        <v>7205991</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -11617,7 +11639,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>96909382</v>
+        <v>96909381</v>
       </c>
       <c r="B114" t="n">
         <v>83173</v>
@@ -11652,10 +11674,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>514187</v>
+        <v>514190</v>
       </c>
       <c r="R114" t="n">
-        <v>7205973</v>
+        <v>7205971</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -11714,7 +11736,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>96909383</v>
+        <v>96909382</v>
       </c>
       <c r="B115" t="n">
         <v>83173</v>
@@ -11749,10 +11771,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>514014</v>
+        <v>514187</v>
       </c>
       <c r="R115" t="n">
-        <v>7206005</v>
+        <v>7205973</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -11811,7 +11833,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>96909384</v>
+        <v>96909383</v>
       </c>
       <c r="B116" t="n">
         <v>83173</v>
@@ -11846,10 +11868,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>513973</v>
+        <v>514014</v>
       </c>
       <c r="R116" t="n">
-        <v>7205987</v>
+        <v>7206005</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -11908,7 +11930,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>96909385</v>
+        <v>96909384</v>
       </c>
       <c r="B117" t="n">
         <v>83173</v>
@@ -11943,10 +11965,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>514373</v>
+        <v>513973</v>
       </c>
       <c r="R117" t="n">
-        <v>7206060</v>
+        <v>7205987</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12005,7 +12027,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>96909386</v>
+        <v>96909385</v>
       </c>
       <c r="B118" t="n">
         <v>83173</v>
@@ -12040,10 +12062,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>514369</v>
+        <v>514373</v>
       </c>
       <c r="R118" t="n">
-        <v>7206072</v>
+        <v>7206060</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12102,7 +12124,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>96909387</v>
+        <v>96909386</v>
       </c>
       <c r="B119" t="n">
         <v>83173</v>
@@ -12137,10 +12159,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>514348</v>
+        <v>514369</v>
       </c>
       <c r="R119" t="n">
-        <v>7206045</v>
+        <v>7206072</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12199,7 +12221,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>96909388</v>
+        <v>96909387</v>
       </c>
       <c r="B120" t="n">
         <v>83173</v>
@@ -12234,10 +12256,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>514303</v>
+        <v>514348</v>
       </c>
       <c r="R120" t="n">
-        <v>7206036</v>
+        <v>7206045</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12296,7 +12318,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130581317</v>
+        <v>96909388</v>
       </c>
       <c r="B121" t="n">
         <v>83173</v>
@@ -12327,14 +12349,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lulevardo, Ås lm</t>
+          <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>513976</v>
+        <v>514303</v>
       </c>
       <c r="R121" t="n">
-        <v>7205648</v>
+        <v>7206036</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12361,22 +12383,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12396,17 +12408,17 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>96909213</v>
+        <v>130581317</v>
       </c>
       <c r="B122" t="n">
-        <v>83312</v>
+        <v>83173</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12414,34 +12426,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Middagskullen, Saxnäs, Ås lm</t>
+          <t>Lulevardo, Ås lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>514123</v>
+        <v>513976</v>
       </c>
       <c r="R122" t="n">
-        <v>7206221</v>
+        <v>7205648</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12468,12 +12480,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12500,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>96909214</v>
+        <v>96909213</v>
       </c>
       <c r="B123" t="n">
         <v>83312</v>
@@ -12535,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>514002</v>
+        <v>514123</v>
       </c>
       <c r="R123" t="n">
-        <v>7206217</v>
+        <v>7206221</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12597,7 +12619,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>96909215</v>
+        <v>96909214</v>
       </c>
       <c r="B124" t="n">
         <v>83312</v>
@@ -12632,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>513980</v>
+        <v>514002</v>
       </c>
       <c r="R124" t="n">
-        <v>7206225</v>
+        <v>7206217</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -12694,7 +12716,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>96909216</v>
+        <v>96909215</v>
       </c>
       <c r="B125" t="n">
         <v>83312</v>
@@ -12729,10 +12751,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>514332</v>
+        <v>513980</v>
       </c>
       <c r="R125" t="n">
-        <v>7206107</v>
+        <v>7206225</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -12759,12 +12781,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12784,14 +12806,14 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>96909218</v>
+        <v>96909216</v>
       </c>
       <c r="B126" t="n">
         <v>83312</v>
@@ -12826,10 +12848,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>513857</v>
+        <v>514332</v>
       </c>
       <c r="R126" t="n">
-        <v>7206042</v>
+        <v>7206107</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -12888,7 +12910,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>96909219</v>
+        <v>96909218</v>
       </c>
       <c r="B127" t="n">
         <v>83312</v>
@@ -12923,10 +12945,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>513858</v>
+        <v>513857</v>
       </c>
       <c r="R127" t="n">
-        <v>7206040</v>
+        <v>7206042</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -12985,7 +13007,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>96909220</v>
+        <v>96909219</v>
       </c>
       <c r="B128" t="n">
         <v>83312</v>
@@ -13020,10 +13042,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>513927</v>
+        <v>513858</v>
       </c>
       <c r="R128" t="n">
-        <v>7206076</v>
+        <v>7206040</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13082,7 +13104,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>96909221</v>
+        <v>96909220</v>
       </c>
       <c r="B129" t="n">
         <v>83312</v>
@@ -13117,10 +13139,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>514191</v>
+        <v>513927</v>
       </c>
       <c r="R129" t="n">
-        <v>7206011</v>
+        <v>7206076</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13179,7 +13201,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>96909222</v>
+        <v>96909221</v>
       </c>
       <c r="B130" t="n">
         <v>83312</v>
@@ -13214,10 +13236,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>514192</v>
+        <v>514191</v>
       </c>
       <c r="R130" t="n">
-        <v>7206007</v>
+        <v>7206011</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13276,7 +13298,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>96909223</v>
+        <v>96909222</v>
       </c>
       <c r="B131" t="n">
         <v>83312</v>
@@ -13311,10 +13333,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>514232</v>
+        <v>514192</v>
       </c>
       <c r="R131" t="n">
-        <v>7206047</v>
+        <v>7206007</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -13373,7 +13395,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>96909224</v>
+        <v>96909223</v>
       </c>
       <c r="B132" t="n">
         <v>83312</v>
@@ -13408,10 +13430,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>514185</v>
+        <v>514232</v>
       </c>
       <c r="R132" t="n">
-        <v>7206023</v>
+        <v>7206047</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -13470,7 +13492,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>96909225</v>
+        <v>96909224</v>
       </c>
       <c r="B133" t="n">
         <v>83312</v>
@@ -13505,10 +13527,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>514227</v>
+        <v>514185</v>
       </c>
       <c r="R133" t="n">
-        <v>7205975</v>
+        <v>7206023</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -13567,7 +13589,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>96909226</v>
+        <v>96909225</v>
       </c>
       <c r="B134" t="n">
         <v>83312</v>
@@ -13602,10 +13624,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>514235</v>
+        <v>514227</v>
       </c>
       <c r="R134" t="n">
-        <v>7205972</v>
+        <v>7205975</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -13664,7 +13686,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>96909227</v>
+        <v>96909226</v>
       </c>
       <c r="B135" t="n">
         <v>83312</v>
@@ -13699,10 +13721,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>514213</v>
+        <v>514235</v>
       </c>
       <c r="R135" t="n">
-        <v>7205982</v>
+        <v>7205972</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -13761,7 +13783,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>96909228</v>
+        <v>96909227</v>
       </c>
       <c r="B136" t="n">
         <v>83312</v>
@@ -13796,10 +13818,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>514150</v>
+        <v>514213</v>
       </c>
       <c r="R136" t="n">
-        <v>7205997</v>
+        <v>7205982</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -13858,7 +13880,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>96909229</v>
+        <v>96909228</v>
       </c>
       <c r="B137" t="n">
         <v>83312</v>
@@ -13893,10 +13915,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>514098</v>
+        <v>514150</v>
       </c>
       <c r="R137" t="n">
-        <v>7205992</v>
+        <v>7205997</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -13955,7 +13977,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>96909230</v>
+        <v>96909229</v>
       </c>
       <c r="B138" t="n">
         <v>83312</v>
@@ -13990,10 +14012,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>514288</v>
+        <v>514098</v>
       </c>
       <c r="R138" t="n">
-        <v>7206076</v>
+        <v>7205992</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14052,32 +14074,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>96909249</v>
+        <v>96909230</v>
       </c>
       <c r="B139" t="n">
-        <v>92292</v>
+        <v>83312</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1506</v>
+        <v>1467</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14087,10 +14109,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>514020</v>
+        <v>514288</v>
       </c>
       <c r="R139" t="n">
-        <v>7206185</v>
+        <v>7206076</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14117,12 +14139,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14142,14 +14164,14 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>96909250</v>
+        <v>96909249</v>
       </c>
       <c r="B140" t="n">
         <v>92292</v>
@@ -14184,10 +14206,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>514263</v>
+        <v>514020</v>
       </c>
       <c r="R140" t="n">
-        <v>7206106</v>
+        <v>7206185</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14214,12 +14236,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14239,17 +14261,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>96909315</v>
+        <v>96909250</v>
       </c>
       <c r="B141" t="n">
-        <v>92283</v>
+        <v>92292</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14257,21 +14279,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2063</v>
+        <v>1506</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14281,10 +14303,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>514182</v>
+        <v>514263</v>
       </c>
       <c r="R141" t="n">
-        <v>7206247</v>
+        <v>7206106</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -14311,12 +14333,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14336,14 +14358,14 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>96909316</v>
+        <v>96909315</v>
       </c>
       <c r="B142" t="n">
         <v>92283</v>
@@ -14378,10 +14400,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>514386</v>
+        <v>514182</v>
       </c>
       <c r="R142" t="n">
-        <v>7206083</v>
+        <v>7206247</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -14408,12 +14430,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14433,39 +14455,39 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>96909199</v>
+        <v>96909316</v>
       </c>
       <c r="B143" t="n">
-        <v>80433</v>
+        <v>92283</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14475,10 +14497,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>514250</v>
+        <v>514386</v>
       </c>
       <c r="R143" t="n">
-        <v>7206165</v>
+        <v>7206083</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -14505,12 +14527,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14530,14 +14552,14 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>96909200</v>
+        <v>96909199</v>
       </c>
       <c r="B144" t="n">
         <v>80433</v>
@@ -14572,10 +14594,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>514248</v>
+        <v>514250</v>
       </c>
       <c r="R144" t="n">
-        <v>7206166</v>
+        <v>7206165</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -14634,7 +14656,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>96909201</v>
+        <v>96909200</v>
       </c>
       <c r="B145" t="n">
         <v>80433</v>
@@ -14669,10 +14691,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>514195</v>
+        <v>514248</v>
       </c>
       <c r="R145" t="n">
-        <v>7206203</v>
+        <v>7206166</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -14731,7 +14753,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96909202</v>
+        <v>96909201</v>
       </c>
       <c r="B146" t="n">
         <v>80433</v>
@@ -14766,10 +14788,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>514082</v>
+        <v>514195</v>
       </c>
       <c r="R146" t="n">
-        <v>7206257</v>
+        <v>7206203</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -14828,7 +14850,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96909203</v>
+        <v>96909202</v>
       </c>
       <c r="B147" t="n">
         <v>80433</v>
@@ -14863,10 +14885,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>514387</v>
+        <v>514082</v>
       </c>
       <c r="R147" t="n">
-        <v>7206014</v>
+        <v>7206257</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -14893,12 +14915,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -14918,14 +14940,14 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>96909204</v>
+        <v>96909203</v>
       </c>
       <c r="B148" t="n">
         <v>80433</v>
@@ -14960,10 +14982,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>513927</v>
+        <v>514387</v>
       </c>
       <c r="R148" t="n">
-        <v>7206098</v>
+        <v>7206014</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15022,7 +15044,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>96909205</v>
+        <v>96909204</v>
       </c>
       <c r="B149" t="n">
         <v>80433</v>
@@ -15057,10 +15079,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>514057</v>
+        <v>513927</v>
       </c>
       <c r="R149" t="n">
-        <v>7206101</v>
+        <v>7206098</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15119,7 +15141,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>96909206</v>
+        <v>96909205</v>
       </c>
       <c r="B150" t="n">
         <v>80433</v>
@@ -15154,10 +15176,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>514248</v>
+        <v>514057</v>
       </c>
       <c r="R150" t="n">
-        <v>7206132</v>
+        <v>7206101</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15216,7 +15238,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>96909207</v>
+        <v>96909206</v>
       </c>
       <c r="B151" t="n">
         <v>80433</v>
@@ -15251,10 +15273,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>514074</v>
+        <v>514248</v>
       </c>
       <c r="R151" t="n">
-        <v>7206094</v>
+        <v>7206132</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -15313,32 +15335,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>96909256</v>
+        <v>96909207</v>
       </c>
       <c r="B152" t="n">
-        <v>96338</v>
+        <v>80433</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15348,10 +15370,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>514199</v>
+        <v>514074</v>
       </c>
       <c r="R152" t="n">
-        <v>7206171</v>
+        <v>7206094</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -15378,12 +15400,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15403,14 +15425,14 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>96909258</v>
+        <v>96909256</v>
       </c>
       <c r="B153" t="n">
         <v>96338</v>
@@ -15445,10 +15467,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>513769</v>
+        <v>514199</v>
       </c>
       <c r="R153" t="n">
-        <v>7206253</v>
+        <v>7206171</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -15507,7 +15529,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>96909259</v>
+        <v>96909258</v>
       </c>
       <c r="B154" t="n">
         <v>96338</v>
@@ -15542,10 +15564,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>514023</v>
+        <v>513769</v>
       </c>
       <c r="R154" t="n">
-        <v>7206217</v>
+        <v>7206253</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -15604,7 +15626,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>96909260</v>
+        <v>96909259</v>
       </c>
       <c r="B155" t="n">
         <v>96338</v>
@@ -15639,10 +15661,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>514057</v>
+        <v>514023</v>
       </c>
       <c r="R155" t="n">
-        <v>7206245</v>
+        <v>7206217</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -15701,7 +15723,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>96909261</v>
+        <v>96909260</v>
       </c>
       <c r="B156" t="n">
         <v>96338</v>
@@ -15736,10 +15758,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>514245</v>
+        <v>514057</v>
       </c>
       <c r="R156" t="n">
-        <v>7206047</v>
+        <v>7206245</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -15766,12 +15788,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -15791,17 +15813,17 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>96909208</v>
+        <v>96909261</v>
       </c>
       <c r="B157" t="n">
-        <v>96350</v>
+        <v>96338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15809,21 +15831,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15833,10 +15855,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>514079</v>
+        <v>514245</v>
       </c>
       <c r="R157" t="n">
-        <v>7206260</v>
+        <v>7206047</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -15863,12 +15885,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -15888,17 +15910,17 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>96909162</v>
+        <v>96909208</v>
       </c>
       <c r="B158" t="n">
-        <v>92632</v>
+        <v>96350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15906,21 +15928,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>2813</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -15930,10 +15952,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>514202</v>
+        <v>514079</v>
       </c>
       <c r="R158" t="n">
-        <v>7206202</v>
+        <v>7206260</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -15992,7 +16014,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>96909163</v>
+        <v>96909162</v>
       </c>
       <c r="B159" t="n">
         <v>92632</v>
@@ -16027,10 +16049,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>513769</v>
+        <v>514202</v>
       </c>
       <c r="R159" t="n">
-        <v>7206254</v>
+        <v>7206202</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16089,7 +16111,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>96909164</v>
+        <v>96909163</v>
       </c>
       <c r="B160" t="n">
         <v>92632</v>
@@ -16124,10 +16146,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>514057</v>
+        <v>513769</v>
       </c>
       <c r="R160" t="n">
-        <v>7206212</v>
+        <v>7206254</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16186,7 +16208,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>96909165</v>
+        <v>96909164</v>
       </c>
       <c r="B161" t="n">
         <v>92632</v>
@@ -16221,10 +16243,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>514217</v>
+        <v>514057</v>
       </c>
       <c r="R161" t="n">
-        <v>7206106</v>
+        <v>7206212</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -16251,12 +16273,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16276,17 +16298,17 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>96909145</v>
+        <v>96909165</v>
       </c>
       <c r="B162" t="n">
-        <v>91872</v>
+        <v>92632</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16294,21 +16316,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16318,10 +16340,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>514080</v>
+        <v>514217</v>
       </c>
       <c r="R162" t="n">
-        <v>7206172</v>
+        <v>7206106</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -16348,12 +16370,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16373,14 +16395,14 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>96909146</v>
+        <v>96909145</v>
       </c>
       <c r="B163" t="n">
         <v>91872</v>
@@ -16415,10 +16437,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>514157</v>
+        <v>514080</v>
       </c>
       <c r="R163" t="n">
-        <v>7205881</v>
+        <v>7206172</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -16445,12 +16467,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16477,7 +16499,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>96909147</v>
+        <v>96909146</v>
       </c>
       <c r="B164" t="n">
         <v>91872</v>
@@ -16512,10 +16534,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>513897</v>
+        <v>514157</v>
       </c>
       <c r="R164" t="n">
-        <v>7205979</v>
+        <v>7205881</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -16567,14 +16589,14 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>96909148</v>
+        <v>96909147</v>
       </c>
       <c r="B165" t="n">
         <v>91872</v>
@@ -16609,10 +16631,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>513891</v>
+        <v>513897</v>
       </c>
       <c r="R165" t="n">
-        <v>7206055</v>
+        <v>7205979</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -16671,7 +16693,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>96909149</v>
+        <v>96909148</v>
       </c>
       <c r="B166" t="n">
         <v>91872</v>
@@ -16706,10 +16728,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>513956</v>
+        <v>513891</v>
       </c>
       <c r="R166" t="n">
-        <v>7205992</v>
+        <v>7206055</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -16768,7 +16790,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>96909150</v>
+        <v>96909149</v>
       </c>
       <c r="B167" t="n">
         <v>91872</v>
@@ -16803,7 +16825,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>513939</v>
+        <v>513956</v>
       </c>
       <c r="R167" t="n">
         <v>7205992</v>
@@ -16865,32 +16887,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>89897928</v>
+        <v>96909150</v>
       </c>
       <c r="B168" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16900,10 +16922,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>514204</v>
+        <v>513939</v>
       </c>
       <c r="R168" t="n">
-        <v>7205588</v>
+        <v>7205992</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -16930,12 +16952,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -16955,14 +16977,14 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>96909347</v>
+        <v>89897928</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -16997,10 +17019,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>514185</v>
+        <v>514204</v>
       </c>
       <c r="R169" t="n">
-        <v>7206224</v>
+        <v>7205588</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -17027,12 +17049,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17059,7 +17081,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>96909354</v>
+        <v>96909347</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -17094,10 +17116,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>514098</v>
+        <v>514185</v>
       </c>
       <c r="R170" t="n">
-        <v>7206172</v>
+        <v>7206224</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17156,7 +17178,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>96909355</v>
+        <v>96909354</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -17191,10 +17213,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>513905</v>
+        <v>514098</v>
       </c>
       <c r="R171" t="n">
-        <v>7206290</v>
+        <v>7206172</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -17253,7 +17275,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>96909356</v>
+        <v>96909355</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -17288,7 +17310,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>513784</v>
+        <v>513905</v>
       </c>
       <c r="R172" t="n">
         <v>7206290</v>
@@ -17350,7 +17372,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>96909357</v>
+        <v>96909356</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -17385,10 +17407,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>513789</v>
+        <v>513784</v>
       </c>
       <c r="R173" t="n">
-        <v>7206264</v>
+        <v>7206290</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -17447,7 +17469,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>96909358</v>
+        <v>96909357</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -17482,10 +17504,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>513777</v>
+        <v>513789</v>
       </c>
       <c r="R174" t="n">
-        <v>7206260</v>
+        <v>7206264</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -17544,7 +17566,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>96909359</v>
+        <v>96909358</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -17579,10 +17601,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>513867</v>
+        <v>513777</v>
       </c>
       <c r="R175" t="n">
-        <v>7206217</v>
+        <v>7206260</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -17641,7 +17663,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>96909360</v>
+        <v>96909359</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -17676,10 +17698,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>514000</v>
+        <v>513867</v>
       </c>
       <c r="R176" t="n">
-        <v>7206182</v>
+        <v>7206217</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -17738,7 +17760,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>96909361</v>
+        <v>96909360</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -17773,10 +17795,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>514123</v>
+        <v>514000</v>
       </c>
       <c r="R177" t="n">
-        <v>7206221</v>
+        <v>7206182</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -17835,7 +17857,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>96909362</v>
+        <v>96909361</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -17870,10 +17892,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>514318</v>
+        <v>514123</v>
       </c>
       <c r="R178" t="n">
-        <v>7205950</v>
+        <v>7206221</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -17900,12 +17922,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -17932,7 +17954,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>96909363</v>
+        <v>96909362</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -17967,10 +17989,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>514212</v>
+        <v>514318</v>
       </c>
       <c r="R179" t="n">
-        <v>7205899</v>
+        <v>7205950</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -18029,7 +18051,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>96909364</v>
+        <v>96909363</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -18064,10 +18086,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>514375</v>
+        <v>514212</v>
       </c>
       <c r="R180" t="n">
-        <v>7206015</v>
+        <v>7205899</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -18126,7 +18148,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>96909365</v>
+        <v>96909364</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -18161,10 +18183,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>514078</v>
+        <v>514375</v>
       </c>
       <c r="R181" t="n">
-        <v>7205849</v>
+        <v>7206015</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -18223,7 +18245,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>96909366</v>
+        <v>96909365</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -18258,10 +18280,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>514005</v>
+        <v>514078</v>
       </c>
       <c r="R182" t="n">
-        <v>7205854</v>
+        <v>7205849</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -18320,7 +18342,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>96909367</v>
+        <v>96909366</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -18355,10 +18377,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>514158</v>
+        <v>514005</v>
       </c>
       <c r="R183" t="n">
-        <v>7205881</v>
+        <v>7205854</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -18417,7 +18439,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>96909368</v>
+        <v>96909367</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -18452,10 +18474,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>513853</v>
+        <v>514158</v>
       </c>
       <c r="R184" t="n">
-        <v>7206001</v>
+        <v>7205881</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -18507,14 +18529,14 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>96909369</v>
+        <v>96909368</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -18549,10 +18571,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>514037</v>
+        <v>513853</v>
       </c>
       <c r="R185" t="n">
-        <v>7206010</v>
+        <v>7206001</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -18611,7 +18633,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96909370</v>
+        <v>96909369</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -18646,10 +18668,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>514398</v>
+        <v>514037</v>
       </c>
       <c r="R186" t="n">
-        <v>7206054</v>
+        <v>7206010</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -18708,7 +18730,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>96909371</v>
+        <v>96909370</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -18743,10 +18765,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>514369</v>
+        <v>514398</v>
       </c>
       <c r="R187" t="n">
-        <v>7206072</v>
+        <v>7206054</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -18805,7 +18827,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>96909372</v>
+        <v>96909371</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -18840,10 +18862,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>514419</v>
+        <v>514369</v>
       </c>
       <c r="R188" t="n">
-        <v>7205998</v>
+        <v>7206072</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -18902,7 +18924,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>96909373</v>
+        <v>96909372</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -18937,10 +18959,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>514288</v>
+        <v>514419</v>
       </c>
       <c r="R189" t="n">
-        <v>7206075</v>
+        <v>7205998</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -18999,7 +19021,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>96909374</v>
+        <v>96909373</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -19034,10 +19056,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>514346</v>
+        <v>514288</v>
       </c>
       <c r="R190" t="n">
-        <v>7206046</v>
+        <v>7206075</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -19096,7 +19118,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>96909375</v>
+        <v>96909374</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -19131,10 +19153,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>514241</v>
+        <v>514346</v>
       </c>
       <c r="R191" t="n">
-        <v>7206030</v>
+        <v>7206046</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -19193,7 +19215,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>98158643</v>
+        <v>96909375</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -19228,10 +19250,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>514200</v>
+        <v>514241</v>
       </c>
       <c r="R192" t="n">
-        <v>7205596</v>
+        <v>7206030</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -19258,22 +19280,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19284,21 +19296,6 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
@@ -19308,14 +19305,14 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130581318</v>
+        <v>98158643</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -19346,14 +19343,14 @@
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lulevardo, Ås lm</t>
+          <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>513975</v>
+        <v>514200</v>
       </c>
       <c r="R193" t="n">
-        <v>7205650</v>
+        <v>7205596</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -19380,22 +19377,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -19406,6 +19403,21 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
@@ -19415,52 +19427,52 @@
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>96909294</v>
+        <v>130581318</v>
       </c>
       <c r="B194" t="n">
-        <v>83290</v>
+        <v>79327</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Middagskullen, Saxnäs, Ås lm</t>
+          <t>Lulevardo, Ås lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>514185</v>
+        <v>513975</v>
       </c>
       <c r="R194" t="n">
-        <v>7206224</v>
+        <v>7205650</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -19487,12 +19499,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19519,7 +19541,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>96909296</v>
+        <v>96909294</v>
       </c>
       <c r="B195" t="n">
         <v>83290</v>
@@ -19554,10 +19576,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>513867</v>
+        <v>514185</v>
       </c>
       <c r="R195" t="n">
-        <v>7206217</v>
+        <v>7206224</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -19616,7 +19638,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>96909297</v>
+        <v>96909296</v>
       </c>
       <c r="B196" t="n">
         <v>83290</v>
@@ -19651,10 +19673,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>514123</v>
+        <v>513867</v>
       </c>
       <c r="R196" t="n">
-        <v>7206221</v>
+        <v>7206217</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -19713,7 +19735,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>96909298</v>
+        <v>96909297</v>
       </c>
       <c r="B197" t="n">
         <v>83290</v>
@@ -19748,10 +19770,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>514002</v>
+        <v>514123</v>
       </c>
       <c r="R197" t="n">
-        <v>7206217</v>
+        <v>7206221</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -19810,7 +19832,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>96909299</v>
+        <v>96909298</v>
       </c>
       <c r="B198" t="n">
         <v>83290</v>
@@ -19845,10 +19867,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>514185</v>
+        <v>514002</v>
       </c>
       <c r="R198" t="n">
-        <v>7206023</v>
+        <v>7206217</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -19875,12 +19897,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -19900,14 +19922,14 @@
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>96909300</v>
+        <v>96909299</v>
       </c>
       <c r="B199" t="n">
         <v>83290</v>
@@ -19942,10 +19964,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>514191</v>
+        <v>514185</v>
       </c>
       <c r="R199" t="n">
-        <v>7206011</v>
+        <v>7206023</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -20004,7 +20026,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>96909301</v>
+        <v>96909300</v>
       </c>
       <c r="B200" t="n">
         <v>83290</v>
@@ -20039,10 +20061,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>514230</v>
+        <v>514191</v>
       </c>
       <c r="R200" t="n">
-        <v>7206049</v>
+        <v>7206011</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -20101,7 +20123,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>96909302</v>
+        <v>96909301</v>
       </c>
       <c r="B201" t="n">
         <v>83290</v>
@@ -20136,10 +20158,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>514192</v>
+        <v>514230</v>
       </c>
       <c r="R201" t="n">
-        <v>7206007</v>
+        <v>7206049</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -20198,7 +20220,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>96909303</v>
+        <v>96909302</v>
       </c>
       <c r="B202" t="n">
         <v>83290</v>
@@ -20233,10 +20255,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>514082</v>
+        <v>514192</v>
       </c>
       <c r="R202" t="n">
-        <v>7205996</v>
+        <v>7206007</v>
       </c>
       <c r="S202" t="n">
         <v>25</v>
@@ -20295,32 +20317,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>96909140</v>
+        <v>96909303</v>
       </c>
       <c r="B203" t="n">
-        <v>83307</v>
+        <v>83290</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20330,10 +20352,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>514377</v>
+        <v>514082</v>
       </c>
       <c r="R203" t="n">
-        <v>7206003</v>
+        <v>7205996</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -20385,14 +20407,14 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>96909141</v>
+        <v>96909140</v>
       </c>
       <c r="B204" t="n">
         <v>83307</v>
@@ -20427,10 +20449,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>514378</v>
+        <v>514377</v>
       </c>
       <c r="R204" t="n">
-        <v>7206016</v>
+        <v>7206003</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -20489,7 +20511,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>96909142</v>
+        <v>96909141</v>
       </c>
       <c r="B205" t="n">
         <v>83307</v>
@@ -20524,10 +20546,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>514398</v>
+        <v>514378</v>
       </c>
       <c r="R205" t="n">
-        <v>7206053</v>
+        <v>7206016</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -20579,14 +20601,14 @@
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>96909143</v>
+        <v>96909142</v>
       </c>
       <c r="B206" t="n">
         <v>83307</v>
@@ -20621,10 +20643,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>514333</v>
+        <v>514398</v>
       </c>
       <c r="R206" t="n">
-        <v>7206054</v>
+        <v>7206053</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -20683,10 +20705,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>96909263</v>
+        <v>96909143</v>
       </c>
       <c r="B207" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20694,21 +20716,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20718,10 +20740,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>514074</v>
+        <v>514333</v>
       </c>
       <c r="R207" t="n">
-        <v>7206095</v>
+        <v>7206054</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -20780,32 +20802,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>96909178</v>
+        <v>96909263</v>
       </c>
       <c r="B208" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -20815,10 +20837,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>514249</v>
+        <v>514074</v>
       </c>
       <c r="R208" t="n">
-        <v>7206166</v>
+        <v>7206095</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -20845,12 +20867,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -20870,14 +20892,14 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>96909179</v>
+        <v>96909178</v>
       </c>
       <c r="B209" t="n">
         <v>80461</v>
@@ -20912,10 +20934,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>514156</v>
+        <v>514249</v>
       </c>
       <c r="R209" t="n">
-        <v>7206238</v>
+        <v>7206166</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -20974,7 +20996,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>96909184</v>
+        <v>96909179</v>
       </c>
       <c r="B210" t="n">
         <v>80461</v>
@@ -21009,10 +21031,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>513769</v>
+        <v>514156</v>
       </c>
       <c r="R210" t="n">
-        <v>7206253</v>
+        <v>7206238</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -21071,7 +21093,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>96909185</v>
+        <v>96909184</v>
       </c>
       <c r="B211" t="n">
         <v>80461</v>
@@ -21106,10 +21128,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>514115</v>
+        <v>513769</v>
       </c>
       <c r="R211" t="n">
-        <v>7206223</v>
+        <v>7206253</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -21168,7 +21190,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>96909186</v>
+        <v>96909185</v>
       </c>
       <c r="B212" t="n">
         <v>80461</v>
@@ -21203,10 +21225,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>514082</v>
+        <v>514115</v>
       </c>
       <c r="R212" t="n">
-        <v>7206257</v>
+        <v>7206223</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -21265,7 +21287,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>96909187</v>
+        <v>96909186</v>
       </c>
       <c r="B213" t="n">
         <v>80461</v>
@@ -21300,10 +21322,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>514057</v>
+        <v>514082</v>
       </c>
       <c r="R213" t="n">
-        <v>7206245</v>
+        <v>7206257</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -21362,7 +21384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>96909188</v>
+        <v>96909187</v>
       </c>
       <c r="B214" t="n">
         <v>80461</v>
@@ -21397,10 +21419,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>513966</v>
+        <v>514057</v>
       </c>
       <c r="R214" t="n">
-        <v>7206236</v>
+        <v>7206245</v>
       </c>
       <c r="S214" t="n">
         <v>25</v>
@@ -21459,7 +21481,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>96909189</v>
+        <v>96909188</v>
       </c>
       <c r="B215" t="n">
         <v>80461</v>
@@ -21494,10 +21516,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>514001</v>
+        <v>513966</v>
       </c>
       <c r="R215" t="n">
-        <v>7205853</v>
+        <v>7206236</v>
       </c>
       <c r="S215" t="n">
         <v>25</v>
@@ -21524,12 +21546,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -21556,7 +21578,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>96909190</v>
+        <v>96909189</v>
       </c>
       <c r="B216" t="n">
         <v>80461</v>
@@ -21591,10 +21613,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>514181</v>
+        <v>514001</v>
       </c>
       <c r="R216" t="n">
-        <v>7205741</v>
+        <v>7205853</v>
       </c>
       <c r="S216" t="n">
         <v>25</v>
@@ -21653,7 +21675,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>96909191</v>
+        <v>96909190</v>
       </c>
       <c r="B217" t="n">
         <v>80461</v>
@@ -21688,10 +21710,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>514267</v>
+        <v>514181</v>
       </c>
       <c r="R217" t="n">
-        <v>7206110</v>
+        <v>7205741</v>
       </c>
       <c r="S217" t="n">
         <v>25</v>
@@ -21743,14 +21765,14 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>96909192</v>
+        <v>96909191</v>
       </c>
       <c r="B218" t="n">
         <v>80461</v>
@@ -21785,10 +21807,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>514387</v>
+        <v>514267</v>
       </c>
       <c r="R218" t="n">
-        <v>7206013</v>
+        <v>7206110</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -21840,14 +21862,14 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>96909193</v>
+        <v>96909192</v>
       </c>
       <c r="B219" t="n">
         <v>80461</v>
@@ -21882,10 +21904,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>514248</v>
+        <v>514387</v>
       </c>
       <c r="R219" t="n">
-        <v>7206132</v>
+        <v>7206013</v>
       </c>
       <c r="S219" t="n">
         <v>25</v>
@@ -21937,14 +21959,14 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>96909194</v>
+        <v>96909193</v>
       </c>
       <c r="B220" t="n">
         <v>80461</v>
@@ -21979,10 +22001,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>514222</v>
+        <v>514248</v>
       </c>
       <c r="R220" t="n">
-        <v>7206054</v>
+        <v>7206132</v>
       </c>
       <c r="S220" t="n">
         <v>25</v>
@@ -22041,7 +22063,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>96909195</v>
+        <v>96909194</v>
       </c>
       <c r="B221" t="n">
         <v>80461</v>
@@ -22076,10 +22098,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>514327</v>
+        <v>514222</v>
       </c>
       <c r="R221" t="n">
-        <v>7206050</v>
+        <v>7206054</v>
       </c>
       <c r="S221" t="n">
         <v>25</v>
@@ -22138,10 +22160,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>96909404</v>
+        <v>96909195</v>
       </c>
       <c r="B222" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22149,21 +22171,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22173,10 +22195,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>514246</v>
+        <v>514327</v>
       </c>
       <c r="R222" t="n">
-        <v>7206131</v>
+        <v>7206050</v>
       </c>
       <c r="S222" t="n">
         <v>25</v>
@@ -22235,10 +22257,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>96909264</v>
+        <v>96909404</v>
       </c>
       <c r="B223" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22246,21 +22268,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22270,10 +22292,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>514245</v>
+        <v>514246</v>
       </c>
       <c r="R223" t="n">
-        <v>7206162</v>
+        <v>7206131</v>
       </c>
       <c r="S223" t="n">
         <v>25</v>
@@ -22300,12 +22322,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -22325,57 +22347,52 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>96909166</v>
+        <v>96909264</v>
       </c>
       <c r="B224" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>514193</v>
+        <v>514245</v>
       </c>
       <c r="R224" t="n">
-        <v>7206262</v>
+        <v>7206162</v>
       </c>
       <c r="S224" t="n">
         <v>25</v>
@@ -22434,7 +22451,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>96909167</v>
+        <v>96909166</v>
       </c>
       <c r="B225" t="n">
         <v>57953</v>
@@ -22474,10 +22491,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>513777</v>
+        <v>514193</v>
       </c>
       <c r="R225" t="n">
-        <v>7206261</v>
+        <v>7206262</v>
       </c>
       <c r="S225" t="n">
         <v>25</v>
@@ -22536,7 +22553,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>96909168</v>
+        <v>96909167</v>
       </c>
       <c r="B226" t="n">
         <v>57953</v>
@@ -22576,10 +22593,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>514409</v>
+        <v>513777</v>
       </c>
       <c r="R226" t="n">
-        <v>7206053</v>
+        <v>7206261</v>
       </c>
       <c r="S226" t="n">
         <v>25</v>
@@ -22606,12 +22623,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -22631,14 +22648,14 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>96909169</v>
+        <v>96909168</v>
       </c>
       <c r="B227" t="n">
         <v>57953</v>
@@ -22678,10 +22695,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>514078</v>
+        <v>514409</v>
       </c>
       <c r="R227" t="n">
-        <v>7205849</v>
+        <v>7206053</v>
       </c>
       <c r="S227" t="n">
         <v>25</v>
@@ -22733,14 +22750,14 @@
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>96909170</v>
+        <v>96909169</v>
       </c>
       <c r="B228" t="n">
         <v>57953</v>
@@ -22780,10 +22797,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>513852</v>
+        <v>514078</v>
       </c>
       <c r="R228" t="n">
-        <v>7206000</v>
+        <v>7205849</v>
       </c>
       <c r="S228" t="n">
         <v>25</v>
@@ -22835,14 +22852,14 @@
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>96909171</v>
+        <v>96909170</v>
       </c>
       <c r="B229" t="n">
         <v>57953</v>
@@ -22882,10 +22899,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>513998</v>
+        <v>513852</v>
       </c>
       <c r="R229" t="n">
-        <v>7205975</v>
+        <v>7206000</v>
       </c>
       <c r="S229" t="n">
         <v>25</v>
@@ -22944,27 +22961,27 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>96909176</v>
+        <v>96909171</v>
       </c>
       <c r="B230" t="n">
-        <v>58592</v>
+        <v>57953</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -22972,14 +22989,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -22988,10 +23001,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>514181</v>
+        <v>513998</v>
       </c>
       <c r="R230" t="n">
-        <v>7205741</v>
+        <v>7205975</v>
       </c>
       <c r="S230" t="n">
         <v>25</v>
@@ -23043,17 +23056,17 @@
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>96909251</v>
+        <v>96909176</v>
       </c>
       <c r="B231" t="n">
-        <v>57144</v>
+        <v>58592</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23061,16 +23074,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>102613</v>
+        <v>102125</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -23078,17 +23091,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>513954</v>
+        <v>514181</v>
       </c>
       <c r="R231" t="n">
-        <v>7206261</v>
+        <v>7205741</v>
       </c>
       <c r="S231" t="n">
         <v>25</v>
@@ -23115,12 +23137,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -23147,10 +23169,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>96909130</v>
+        <v>96909251</v>
       </c>
       <c r="B232" t="n">
-        <v>106229</v>
+        <v>57144</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23158,21 +23180,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23182,10 +23204,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514205</v>
+        <v>513954</v>
       </c>
       <c r="R232" t="n">
-        <v>7206159</v>
+        <v>7206261</v>
       </c>
       <c r="S232" t="n">
         <v>25</v>
@@ -23244,7 +23266,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>96909131</v>
+        <v>96909130</v>
       </c>
       <c r="B233" t="n">
         <v>106229</v>
@@ -23279,10 +23301,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514025</v>
+        <v>514205</v>
       </c>
       <c r="R233" t="n">
-        <v>7206216</v>
+        <v>7206159</v>
       </c>
       <c r="S233" t="n">
         <v>25</v>
@@ -23341,10 +23363,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>96909246</v>
+        <v>96909131</v>
       </c>
       <c r="B234" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23352,21 +23374,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23376,10 +23398,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>514123</v>
+        <v>514025</v>
       </c>
       <c r="R234" t="n">
-        <v>7206222</v>
+        <v>7206216</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -23438,7 +23460,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>96909247</v>
+        <v>96909246</v>
       </c>
       <c r="B235" t="n">
         <v>97983</v>
@@ -23473,10 +23495,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>514156</v>
+        <v>514123</v>
       </c>
       <c r="R235" t="n">
-        <v>7206238</v>
+        <v>7206222</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -23535,48 +23557,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>98158648</v>
+        <v>96909247</v>
       </c>
       <c r="B236" t="n">
-        <v>78333</v>
+        <v>97983</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>228575</v>
+        <v>221945</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Brun svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Chaenothecopsis epithallina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514204</v>
+        <v>514156</v>
       </c>
       <c r="R236" t="n">
-        <v>7205580</v>
+        <v>7206238</v>
       </c>
       <c r="S236" t="n">
         <v>25</v>
@@ -23603,22 +23622,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -23627,34 +23636,8 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>grå nållav</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Chaenotheca trichialis</t>
-        </is>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>Chaenotheca trichialis</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>2201161140</t>
-        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
@@ -23664,17 +23647,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>96909273</v>
+        <v>98158648</v>
       </c>
       <c r="B237" t="n">
-        <v>92329</v>
+        <v>78333</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23682,34 +23665,37 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6040186</v>
+        <v>228575</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Brun svartspik</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenothecopsis epithallina</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Middagskullen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>513872</v>
+        <v>514204</v>
       </c>
       <c r="R237" t="n">
-        <v>7206316</v>
+        <v>7205580</v>
       </c>
       <c r="S237" t="n">
         <v>25</v>
@@ -23736,12 +23722,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-01-16</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -23750,8 +23746,34 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>grå nållav</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Chaenotheca trichialis</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>Chaenotheca trichialis</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>2201161140</t>
+        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
@@ -23761,10 +23783,107 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Sara Öhrnell</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>96909273</v>
+      </c>
+      <c r="B238" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Middagskullen, Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>513872</v>
+      </c>
+      <c r="R238" t="n">
+        <v>7206316</v>
+      </c>
+      <c r="S238" t="n">
+        <v>25</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
